--- a/data/daily/2026-09/2026-09-16.xlsx
+++ b/data/daily/2026-09/2026-09-16.xlsx
@@ -11,7 +11,9 @@
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="다이소몰" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="다이소몰_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="올리브영" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="올리브영_카드형" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="카테고리통계" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1218,7 +1220,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="323850" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1243,7 +1245,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="323850" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1268,14 +1270,64 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1290,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1315,85 +1367,35 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1473,7 +1475,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1498,7 +1500,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1523,9 +1525,264 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1543,12 +1800,267 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1573,7 +2085,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1598,7 +2110,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1623,7 +2135,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1648,7 +2160,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2084,23 +2596,19 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16054</v>
+        <v>16055</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 선물로 받았을 때 기분이 좋고 생일 및 응원용 선물로 매우 적합함</t>
+          <t>선물용 우수한 구성 — 선물로 받을 때 만족도가 높고 다양한 감사 및 응원 선물로 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>면역력 및 건강 케어 — 꾸준히 섭취 시 면역력 증진 및 건강 유지에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>고급스러운 브랜드 이미지 — 비타민계의 에르메스로 불릴 정도로 선물 가치가 높음</t>
-        </is>
-      </c>
+          <t>면역력 강화 기대 — 피로 회복과 면역력 증진에 도움을 줄 것으로 기대됨</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2147,17 +2655,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>달콤하고 맛있는 제형 — 비타민 특유의 신맛 대신 달콤한 과일 맛이 나 맛이 좋음</t>
+          <t>달콤하고 맛있는 풍미 — 비타민 특유의 신맛 없이 달콤한 과일 맛이 남</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>깔끔한 선물 패키지 — 네이비와 오렌지 컬러 조합의 고급스러운 패키지와 깔끔한 포장으로 전달됨</t>
+          <t>고급스러운 포장 디자인 — 네이비와 오렌지 컬러의 패키지가 깔끔하고 고급스러움</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>휴대 및 섭취 편의성 — 작은 용기에 들어 있어 휴대하기 좋고 간편하게 먹기 편함</t>
+          <t>편리한 휴대성 — 작은 용기로 구성되어 편리하게 휴대하며 섭취 가능함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2206,18 +2714,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 — 섭취 후 피로감이 줄어들고 컨디션 회복에 도움이 됨</t>
+          <t>뛰어난 피로 회복 효과 — 복용 후 피로감이 줄어들고 힘이 나는 느낌을 받음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>맛있고 고급스러운 포장 — 맛이 좋아 섭취 부담이 없고 고급스럽게 포장되어 배송됨</t>
+          <t>고급스러운 포장 상태 — 포장이 고급스럽게 잘 되어 있어 선물용으로 우수함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>구매 후 가격 하락 — 제품 구매 후 가격이 내려가 아쉬움이 남음</t>
+          <t>구매 후 가격 인하 — 구매 직후 제품 가격이 내려가 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2265,17 +2773,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>피로 회복 및 생기 충전 — 피로감이 덜하고 회복 기간 동안 생기를 찾기 좋음</t>
+          <t>빠른 피로 회복 느낌 — 복용 후 피로가 덜하고 생기 회복에 도움이 됨</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 — 다양한 영양소를 한 번에 간편하게 챙길 수 있어 유용함</t>
+          <t>간편한 일체형 구성 — 여러 영양제를 따로 챙길 필요 없이 한 번에 간편하게 섭취함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>알찬 추가 증정 구성 — 선물하기 전용 구성으로 추가 증정이 포함되어 만족스러움</t>
+          <t>알찬 추가 증정 혜택 — 7입 구성에 2입이 추가 증정되어 더욱 실용적임</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2324,17 +2832,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 선물용 포장이 이쁘고 고급스러워 전달 시 만족도가 높음</t>
+          <t>고급스러운 선물용 포장 — 선물 포장이 예쁘고 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>쉬운 알약 목넘김 — 알약 크기가 크지 않아 삼키기 수월함</t>
+          <t>쉬운 알약 목넘김 — 알약 크기가 크지 않아 쉽게 삼킬 수 있음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>간편한 피로 관리 — 바쁜 일상에서 종합 영양을 한 번에 챙겨 피로 회복에 도움됨</t>
+          <t>빠른 컨디션 회복 — 피로할 때 섭취하면 컨디션 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2383,23 +2891,23 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 맛있는 구미 형태라 알약 거부감 없이 챙겨 먹기 좋음</t>
+          <t>맛있는 젤리 제형 — 알약 거부감 없이 맛있는 젤리처럼 손이 자주 감</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>남녀노소 높은 선호도 — 아이들도 좋아하고 간식처럼 부담 없이 복용 가능함</t>
+          <t>간편한 복용 방법 — 하루 2개씩 씹어 먹으면 되어 복용이 간편함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>약간의 씁쓸한 맛 — 단맛이 과하지 않고 끝맛에 약간의 씁쓸함이 느껴짐</t>
+          <t>약간의 씁쓸한 맛 — 달지 않고 약간 씁쓸한 맛이 느껴짐</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>모호한 체감 효과 — 섭취 후 뚜렷한 효과를 직접 체감하기 어려움</t>
+          <t>효과 체감의 불확실성 — 실제 효과가 있는지 직접 체감하기 어려움</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -2446,16 +2954,20 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 — 피로감이 심할 때 섭취 시 컨디션 회복에 큰 도움됨</t>
+          <t>우수한 컨디션 회복 — 피로감이 심할 때 섭취 시 컨디션 회복에 효과적임</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>간편한 마시는 제형 — 액상 형태로 마시기 편하고 휴대성이 뛰어남</t>
+          <t>편리한 휴대 및 섭취 — 휴대하기 편하고 간편하게 마시기 좋은 형태임</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>다소 높은 가격대 — 가격대가 높아 지속적 구매에 부담이 될 수 있음</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -2501,17 +3013,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>브랜드 신뢰와 고급 포장 — 정관장 브랜드 신뢰감이 크고 포장이 매우 고급스러움</t>
+          <t>고급스러운 패키지 — 포장이 고급스러워 선물용으로 만족도가 매우 높음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 달콤새콤한 맛 — 쓴맛이 강하지 않고 달콤새콤하여 부담 없이 먹기 좋음</t>
+          <t>부담 없는 상큼한 맛 — 쓴맛 없이 달달하고 새콤하여 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성 — 가방이나 주머니에 넣고 다니며 간편하게 챙겨 먹기 편함</t>
+          <t>높은 브랜드 신뢰도 — 정관장 브랜드 제품으로 믿고 먹을 수 있음</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -2560,19 +3072,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>체감되는 피로 완화 — 피로감이 덜하고 개운한 하루를 보내는 데 도움이 됨</t>
+          <t>체감되는 피로 개선 — 피로감이 덜해지고 개운한 상태를 유지하는 데 도움 됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>고급스러운 추석 패키지 — 패키지 구성이 고급스럽고 귀여운 사은품이 포함됨</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>맛있는 액상 타입 — 맛이 좋아 피곤할 때마다 간편하고 맛있게 마시기 좋음</t>
-        </is>
-      </c>
+          <t>고급스러운 패키지 — 명절 패키지가 고급스럽고 젤리까지 동봉되어 구성이 알참</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -2619,22 +3127,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>꾸준한 피로 회복 효과 — 지속적으로 섭취 시 피로함이 덜하고 효과가 나타남</t>
+          <t>효과적인 피로 감소 — 꾸준히 복용 시 피로함이 덜하고 효과를 체감함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>우수한 포장과 디자인 — 포장이 깔끔하고 성의가 보여 선물받을 때 기분이 좋음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>편리한 휴대성 — 하루 하나씩 챙겨 먹기 편하고 휴대하기 용이함</t>
-        </is>
-      </c>
+          <t>우수한 휴대성 — 하루 하나씩 가지고 다니며 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>삼키기 힘든 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
+          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 약간 힘듦</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2678,20 +3182,24 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>맛있는 말차베리 맛 — 효소 특유의 역함 없이 말차향이 은은하여 맛있게 먹기 좋음</t>
+          <t>맛있는 말차베리 풍미 — 말차향이 과하지 않고 맛있게 즐길 수 있음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>만족스러운 사은품 구성 — 포토카드와 엽서 등 팬심을 채워주는 다양한 사은품이 제공됨</t>
+          <t>만족스러운 굿즈 구성 — 포토카드와 엽서 등 만족스러운 굿즈가 동봉됨</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>기존 대비 적은 용량 — 기존 효소 제품에 비해 용량이 절반 수준으로 적음</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -2737,17 +3245,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>원활한 소화 및 배변 — 식후 더부룩함이 줄어들고 배변 활동에 도움을 줌</t>
+          <t>우수한 소화 및 배변 — 식후 복용 시 소화가 잘되고 배변 활동에 도움을 줌</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>고소한 군고구마 맛 — 맛이 고소하고 군고구마 맛이 나 부담 없이 복용 가능함</t>
+          <t>고소한 군고구마 맛 — 고소하고 군고구마 맛이 나 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>합리적 가격과 풍부한 증정 — 할인 이벤트와 사은품 증정이 풍부하여 가성비가 훌륭함</t>
+          <t>합리적인 가격 혜택 — 할인 행사 및 사은품 증정 혜택으로 가격 부담이 적음</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2796,19 +3304,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 패키지 — 오간자 에디션 포장이 정성스럽고 고급스러움을 줌</t>
+          <t>정성스러운 고급 포장 — 포장이 예쁘고 고급스러워 선물용으로 매우 만족스러움</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>피부 개선 체감 — 피부가 맑아지고 탱탱해지는 듯한 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>편리한 섭취 방식 — 용기가 예쁘고 앰플 타입으로 간편하게 섭취 가능함</t>
-        </is>
-      </c>
+          <t>피부 개선 기대감 — 복용 시 피부가 맑아지고 탱탱해지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2855,23 +3359,23 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>좋은 맛과 섭취 편의성 — 맛도 괜찮고 포장이 고급스러우며 복용하기 편함</t>
+          <t>맛과 소화 촉진 효과 — 맛이 좋고 식후 소화 관리에 도움을 줌</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>알찬 사은품 증정 구성 — 저렴한 가격에 추가 증정 10포 및 과자가 제공됨</t>
+          <t>보너스 증정 혜택 — 추가 증정 10포와 과자 사은품 구성이 알참</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>구매 수량 제한 — 1회 구매 시 2개 이상 주문이 불가능하여 아쉬움</t>
+          <t>구매 수량 제한 — 구매 수량이 최대 2개로 제한되어 있어 아쉬움</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>복용 초기 장내 가스 발생 — 복용 후 뱃속이 꾸룩거리거나 방귀가 나오는 현상이 있음</t>
+          <t>복용 초기 장 반응 — 복용 직후 뱃속이 꾸르룩거리고 방귀가 자주 나옴</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -2918,22 +3422,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>부드럽고 맛있는 식감 — 뻑뻑함이 적고 부드러우며 양념이 자극적이지 않고 맛있음</t>
+          <t>부드럽고 맛있는 식감 — 닭가슴살의 뻑뻑함 없이 부드럽고 맛있음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>다양한 구성과 가성비 — 메뉴가 다양하여 물리지 않고 저렴한 가격 대비 수량이 알참</t>
+          <t>다양한 맛 구성 — 다양한 맛으로 구성되어 매일 먹어도 물리지 않음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>간편한 조리 방법 — 전자레인지 조리로 쉽고 편리하게 식단 관리가 가능함</t>
+          <t>뛰어난 가성비 — 24팩의 닭가슴살을 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>배송 중 해동 상태 — 제품 배송 과정에서 완전히 녹아서 도착함</t>
+          <t>배송 중 제품 융해 — 배송 시 제품이 완전히 녹아서 도착하는 문제 있음</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2981,27 +3485,23 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>다채로운 맛 구성 — 종류가 다양하여 매일 골라 먹는 재미가 있고 물리지 않음</t>
+          <t>다양하고 알찬 구성 — 종류가 다양하여 매일 하나씩 골라 먹는 재미가 있음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>보냉백 증정 혜택 — 증정되는 보냉 파우치로 도시락을 싸 들고 다니기 유용함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 한 달 식단 분량을 합리적인 가격에 구매 가능함</t>
-        </is>
-      </c>
+          <t>유용한 증정 사은품 — 도시락 싸기에 용이한 보냉백을 증정하여 유용함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>포장 불량 및 제품 터짐 — 진공 포장이 헐렁하거나 봉지가 터져 소스가 묻어남</t>
+          <t>포장 불량 및 터짐 — 일부 포장이 터져 소스가 새고 진공 상태가 헐렁함</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>배송 중 해동 상태 — 배송 시 제품이 많이 녹아내린 상태로 도착함</t>
+          <t>배송 중 제품 해동 — 도착 시 제품이 많이 녹아 있음</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -3048,17 +3548,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>텁텁함 없는 깔끔한 맛 — 단백질 음료 특유의 비린맛이나 텁텁함 없이 부드럽고 달콤함</t>
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 텁텁함과 비린 맛 없이 음료처럼 맛있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>든든한 포만감과 낮은 당 — 당과 칼로리가 낮아 다이어트에 부담이 없고 포만감이 유지됨</t>
+          <t>부드러운 목넘김 — 목넘김이 부드럽고 마신 후 속이 더부룩하지 않음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>우수한 휴대성 — 패키지가 슬림하여 가방에 넣고 들고 다니며 마시기 편함</t>
+          <t>알찬 영양 성분 — 당과 칼로리가 낮고 팩당 단백질 함량이 20g으로 충분함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3107,17 +3607,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 아침 공복 섭취 시 하루 시작이 가벼워지고 피로가 개선됨</t>
+          <t>빠른 피로 회복 효과 — 섭취 후 에너지가 생기고 피로 회복에 도움이 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 액상 — 물에 타먹기 편하고 거부감 없는 상큼한 레몬맛임</t>
+          <t>상큼한 레몬맛 — 부담 없는 레몬맛으로 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>간편한 휴대성 — 액상 스틱 타입이라 외출 시 챙겨 나가기 용이함</t>
+          <t>편리한 액상 제형 — 물에 타 먹거나 간편하게 챙기기 좋은 액상 스틱 제형임</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3166,17 +3666,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>초고함량 아르기닌 효과 — 6,200mg 고함량으로 피로도가 낮아지고 운동 퍼포먼스가 향상됨</t>
+          <t>고함량으로 인한 활력 — 6,200mg 고함량 아르기닌으로 운동 및 일상 활력 증진에 효과적임</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 블랙 및 레드 조합 패키지와 전용 쇼핑백, 추가 포 증정이 만족스러움</t>
+          <t>알찬 추가 증정 구성 — 쇼핑백과 추가 5포 증정으로 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>간편한 1일 1포 섭취 — 개별 포장되어 있어 들고 다니기 좋고 하루 한 포로 간편함</t>
+          <t>편리한 개별 포장 — 개별 포장되어 있어 휴대와 복용이 용이함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3225,17 +3725,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>신뢰도 높은 조합 구성 — 아르기닌과 밀크씨슬 및 마카를 한 번에 챙겨 활력 충전에 효과적임</t>
+          <t>알찬 세트 조합 — 아르기닌과 밀크씨슬/마카 세트로 건강을 한 번에 관리함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>지속적인 피로 개선 — 아침에 몸이 덜 무겁고 하루 동안 활력과 집중력이 오래 유지됨</t>
+          <t>피로 감소 및 활력 — 아침에 일어날 때 몸이 가볍고 피로감이 감소함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>넉넉한 용량과 쇼핑백 — 2개월분 구성으로 넉넉하며 쇼핑백이 함께 와 선물하기에 좋음</t>
+          <t>넉넉한 2개월 용량 — 2개월분의 넉넉한 용량 구성으로 만족스러움</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3560,7 +4060,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16054</v>
+        <v>16055</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15392</v>
@@ -3598,69 +4098,66 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 선물로 받았을 때 기분이 좋고 생일 및 응원용 선물로 매우 적합함
-면역력 및 건강 케어 — 꾸준히 섭취 시 면역력 증진 및 건강 유지에 도움이 됨
-고급스러운 브랜드 이미지 — 비타민계의 에르메스로 불릴 정도로 선물 가치가 높음</t>
+          <t>선물용 우수한 구성 — 선물로 받을 때 만족도가 높고 다양한 감사 및 응원 선물로 적합함
+면역력 강화 기대 — 피로 회복과 면역력 증진에 도움을 줄 것으로 기대됨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>달콤하고 맛있는 제형 — 비타민 특유의 신맛 대신 달콤한 과일 맛이 나 맛이 좋음
-깔끔한 선물 패키지 — 네이비와 오렌지 컬러 조합의 고급스러운 패키지와 깔끔한 포장으로 전달됨
-휴대 및 섭취 편의성 — 작은 용기에 들어 있어 휴대하기 좋고 간편하게 먹기 편함</t>
+          <t>달콤하고 맛있는 풍미 — 비타민 특유의 신맛 없이 달콤한 과일 맛이 남
+고급스러운 포장 디자인 — 네이비와 오렌지 컬러의 패키지가 깔끔하고 고급스러움
+편리한 휴대성 — 작은 용기로 구성되어 편리하게 휴대하며 섭취 가능함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 — 섭취 후 피로감이 줄어들고 컨디션 회복에 도움이 됨
-맛있고 고급스러운 포장 — 맛이 좋아 섭취 부담이 없고 고급스럽게 포장되어 배송됨</t>
+          <t>뛰어난 피로 회복 효과 — 복용 후 피로감이 줄어들고 힘이 나는 느낌을 받음
+고급스러운 포장 상태 — 포장이 고급스럽게 잘 되어 있어 선물용으로 우수함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 생기 충전 — 피로감이 덜하고 회복 기간 동안 생기를 찾기 좋음
-간편한 올인원 섭취 — 다양한 영양소를 한 번에 간편하게 챙길 수 있어 유용함
-알찬 추가 증정 구성 — 선물하기 전용 구성으로 추가 증정이 포함되어 만족스러움</t>
+          <t>빠른 피로 회복 느낌 — 복용 후 피로가 덜하고 생기 회복에 도움이 됨
+간편한 일체형 구성 — 여러 영양제를 따로 챙길 필요 없이 한 번에 간편하게 섭취함
+알찬 추가 증정 혜택 — 7입 구성에 2입이 추가 증정되어 더욱 실용적임</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 선물용 포장이 이쁘고 고급스러워 전달 시 만족도가 높음
-쉬운 알약 목넘김 — 알약 크기가 크지 않아 삼키기 수월함
-간편한 피로 관리 — 바쁜 일상에서 종합 영양을 한 번에 챙겨 피로 회복에 도움됨</t>
+          <t>고급스러운 선물용 포장 — 선물 포장이 예쁘고 고급스러워 선물용으로 적합함
+쉬운 알약 목넘김 — 알약 크기가 크지 않아 쉽게 삼킬 수 있음
+빠른 컨디션 회복 — 피로할 때 섭취하면 컨디션 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 맛있는 구미 형태라 알약 거부감 없이 챙겨 먹기 좋음
-남녀노소 높은 선호도 — 아이들도 좋아하고 간식처럼 부담 없이 복용 가능함</t>
+          <t>맛있는 젤리 제형 — 알약 거부감 없이 맛있는 젤리처럼 손이 자주 감
+간편한 복용 방법 — 하루 2개씩 씹어 먹으면 되어 복용이 간편함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 — 피로감이 심할 때 섭취 시 컨디션 회복에 큰 도움됨
-간편한 마시는 제형 — 액상 형태로 마시기 편하고 휴대성이 뛰어남</t>
+          <t>우수한 컨디션 회복 — 피로감이 심할 때 섭취 시 컨디션 회복에 효과적임
+편리한 휴대 및 섭취 — 휴대하기 편하고 간편하게 마시기 좋은 형태임</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>브랜드 신뢰와 고급 포장 — 정관장 브랜드 신뢰감이 크고 포장이 매우 고급스러움
-부담 없는 달콤새콤한 맛 — 쓴맛이 강하지 않고 달콤새콤하여 부담 없이 먹기 좋음
-뛰어난 휴대성 — 가방이나 주머니에 넣고 다니며 간편하게 챙겨 먹기 편함</t>
+          <t>고급스러운 패키지 — 포장이 고급스러워 선물용으로 만족도가 매우 높음
+부담 없는 상큼한 맛 — 쓴맛 없이 달달하고 새콤하여 부담 없이 먹기 좋음
+높은 브랜드 신뢰도 — 정관장 브랜드 제품으로 믿고 먹을 수 있음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 완화 — 피로감이 덜하고 개운한 하루를 보내는 데 도움이 됨
-고급스러운 추석 패키지 — 패키지 구성이 고급스럽고 귀여운 사은품이 포함됨
-맛있는 액상 타입 — 맛이 좋아 피곤할 때마다 간편하고 맛있게 마시기 좋음</t>
+          <t>체감되는 피로 개선 — 피로감이 덜해지고 개운한 상태를 유지하는 데 도움 됨
+고급스러운 패키지 — 명절 패키지가 고급스럽고 젤리까지 동봉되어 구성이 알참</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>꾸준한 피로 회복 효과 — 지속적으로 섭취 시 피로함이 덜하고 효과가 나타남
-우수한 포장과 디자인 — 포장이 깔끔하고 성의가 보여 선물받을 때 기분이 좋음
-편리한 휴대성 — 하루 하나씩 챙겨 먹기 편하고 휴대하기 용이함</t>
+          <t>효과적인 피로 감소 — 꾸준히 복용 시 피로함이 덜하고 효과를 체감함
+우수한 휴대성 — 하루 하나씩 가지고 다니며 먹기 편함</t>
         </is>
       </c>
     </row>
@@ -3674,23 +4171,27 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>구매 후 가격 하락 — 제품 구매 후 가격이 내려가 아쉬움이 남음</t>
+          <t>구매 후 가격 인하 — 구매 직후 제품 가격이 내려가 아쉬움이 남음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>약간의 씁쓸한 맛 — 단맛이 과하지 않고 끝맛에 약간의 씁쓸함이 느껴짐
-모호한 체감 효과 — 섭취 후 뚜렷한 효과를 직접 체감하기 어려움</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+          <t>약간의 씁쓸한 맛 — 달지 않고 약간 씁쓸한 맛이 느껴짐
+효과 체감의 불확실성 — 실제 효과가 있는지 직접 체감하기 어려움</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>다소 높은 가격대 — 가격대가 높아 지속적 구매에 부담이 될 수 있음</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>삼키기 힘든 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
+          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 약간 힘듦</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4598,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1655</v>
@@ -4135,70 +4636,68 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 말차베리 맛 — 효소 특유의 역함 없이 말차향이 은은하여 맛있게 먹기 좋음
-만족스러운 사은품 구성 — 포토카드와 엽서 등 팬심을 채워주는 다양한 사은품이 제공됨</t>
+          <t>맛있는 말차베리 풍미 — 말차향이 과하지 않고 맛있게 즐길 수 있음
+만족스러운 굿즈 구성 — 포토카드와 엽서 등 만족스러운 굿즈가 동봉됨</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>원활한 소화 및 배변 — 식후 더부룩함이 줄어들고 배변 활동에 도움을 줌
-고소한 군고구마 맛 — 맛이 고소하고 군고구마 맛이 나 부담 없이 복용 가능함
-합리적 가격과 풍부한 증정 — 할인 이벤트와 사은품 증정이 풍부하여 가성비가 훌륭함</t>
+          <t>우수한 소화 및 배변 — 식후 복용 시 소화가 잘되고 배변 활동에 도움을 줌
+고소한 군고구마 맛 — 고소하고 군고구마 맛이 나 부담 없이 먹기 좋음
+합리적인 가격 혜택 — 할인 행사 및 사은품 증정 혜택으로 가격 부담이 적음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 패키지 — 오간자 에디션 포장이 정성스럽고 고급스러움을 줌
-피부 개선 체감 — 피부가 맑아지고 탱탱해지는 듯한 느낌을 받음
-편리한 섭취 방식 — 용기가 예쁘고 앰플 타입으로 간편하게 섭취 가능함</t>
+          <t>정성스러운 고급 포장 — 포장이 예쁘고 고급스러워 선물용으로 매우 만족스러움
+피부 개선 기대감 — 복용 시 피부가 맑아지고 탱탱해지는 느낌을 받음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>좋은 맛과 섭취 편의성 — 맛도 괜찮고 포장이 고급스러우며 복용하기 편함
-알찬 사은품 증정 구성 — 저렴한 가격에 추가 증정 10포 및 과자가 제공됨</t>
+          <t>맛과 소화 촉진 효과 — 맛이 좋고 식후 소화 관리에 도움을 줌
+보너스 증정 혜택 — 추가 증정 10포와 과자 사은품 구성이 알참</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 맛있는 식감 — 뻑뻑함이 적고 부드러우며 양념이 자극적이지 않고 맛있음
-다양한 구성과 가성비 — 메뉴가 다양하여 물리지 않고 저렴한 가격 대비 수량이 알참
-간편한 조리 방법 — 전자레인지 조리로 쉽고 편리하게 식단 관리가 가능함</t>
+          <t>부드럽고 맛있는 식감 — 닭가슴살의 뻑뻑함 없이 부드럽고 맛있음
+다양한 맛 구성 — 다양한 맛으로 구성되어 매일 먹어도 물리지 않음
+뛰어난 가성비 — 24팩의 닭가슴살을 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 맛 구성 — 종류가 다양하여 매일 골라 먹는 재미가 있고 물리지 않음
-보냉백 증정 혜택 — 증정되는 보냉 파우치로 도시락을 싸 들고 다니기 유용함
-뛰어난 가성비 — 한 달 식단 분량을 합리적인 가격에 구매 가능함</t>
+          <t>다양하고 알찬 구성 — 종류가 다양하여 매일 하나씩 골라 먹는 재미가 있음
+유용한 증정 사은품 — 도시락 싸기에 용이한 보냉백을 증정하여 유용함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>텁텁함 없는 깔끔한 맛 — 단백질 음료 특유의 비린맛이나 텁텁함 없이 부드럽고 달콤함
-든든한 포만감과 낮은 당 — 당과 칼로리가 낮아 다이어트에 부담이 없고 포만감이 유지됨
-우수한 휴대성 — 패키지가 슬림하여 가방에 넣고 들고 다니며 마시기 편함</t>
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 텁텁함과 비린 맛 없이 음료처럼 맛있음
+부드러운 목넘김 — 목넘김이 부드럽고 마신 후 속이 더부룩하지 않음
+알찬 영양 성분 — 당과 칼로리가 낮고 팩당 단백질 함량이 20g으로 충분함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 아침 공복 섭취 시 하루 시작이 가벼워지고 피로가 개선됨
-상큼한 레몬맛 액상 — 물에 타먹기 편하고 거부감 없는 상큼한 레몬맛임
-간편한 휴대성 — 액상 스틱 타입이라 외출 시 챙겨 나가기 용이함</t>
+          <t>빠른 피로 회복 효과 — 섭취 후 에너지가 생기고 피로 회복에 도움이 됨
+상큼한 레몬맛 — 부담 없는 레몬맛으로 맛있게 섭취 가능함
+편리한 액상 제형 — 물에 타 먹거나 간편하게 챙기기 좋은 액상 스틱 제형임</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>초고함량 아르기닌 효과 — 6,200mg 고함량으로 피로도가 낮아지고 운동 퍼포먼스가 향상됨
-고급스러운 선물 포장 — 블랙 및 레드 조합 패키지와 전용 쇼핑백, 추가 포 증정이 만족스러움
-간편한 1일 1포 섭취 — 개별 포장되어 있어 들고 다니기 좋고 하루 한 포로 간편함</t>
+          <t>고함량으로 인한 활력 — 6,200mg 고함량 아르기닌으로 운동 및 일상 활력 증진에 효과적임
+알찬 추가 증정 구성 — 쇼핑백과 추가 5포 증정으로 선물용으로 적합함
+편리한 개별 포장 — 개별 포장되어 있어 휴대와 복용이 용이함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>신뢰도 높은 조합 구성 — 아르기닌과 밀크씨슬 및 마카를 한 번에 챙겨 활력 충전에 효과적임
-지속적인 피로 개선 — 아침에 몸이 덜 무겁고 하루 동안 활력과 집중력이 오래 유지됨
-넉넉한 용량과 쇼핑백 — 2개월분 구성으로 넉넉하며 쇼핑백이 함께 와 선물하기에 좋음</t>
+          <t>알찬 세트 조합 — 아르기닌과 밀크씨슬/마카 세트로 건강을 한 번에 관리함
+피로 감소 및 활력 — 아침에 일어날 때 몸이 가볍고 피로감이 감소함
+넉넉한 2개월 용량 — 2개월분의 넉넉한 용량 구성으로 만족스러움</t>
         </is>
       </c>
     </row>
@@ -4208,24 +4707,28 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>기존 대비 적은 용량 — 기존 효소 제품에 비해 용량이 절반 수준으로 적음</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>구매 수량 제한 — 1회 구매 시 2개 이상 주문이 불가능하여 아쉬움
-복용 초기 장내 가스 발생 — 복용 후 뱃속이 꾸룩거리거나 방귀가 나오는 현상이 있음</t>
+          <t>구매 수량 제한 — 구매 수량이 최대 2개로 제한되어 있어 아쉬움
+복용 초기 장 반응 — 복용 직후 뱃속이 꾸르룩거리고 방귀가 자주 나옴</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 해동 상태 — 제품 배송 과정에서 완전히 녹아서 도착함</t>
+          <t>배송 중 제품 융해 — 배송 시 제품이 완전히 녹아서 도착하는 문제 있음</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>포장 불량 및 제품 터짐 — 진공 포장이 헐렁하거나 봉지가 터져 소스가 묻어남
-배송 중 해동 상태 — 배송 시 제품이 많이 녹아내린 상태로 도착함</t>
+          <t>포장 불량 및 터짐 — 일부 포장이 터져 소스가 새고 진공 상태가 헐렁함
+배송 중 제품 해동 — 도착 시 제품이 많이 녹아 있음</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -4484,12 +4987,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
+          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4499,34 +5002,34 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591420&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235549&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250514/oMFpSUTevplZ5wvdXiLh591591420_00_00oMFpSUTevplZ5wvdXiLh.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/kQh0cYBVEEUhZLYsuKrQ968235549_00_00kQh0cYBVEEUhZLYsuKrQ.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>254</v>
+        <v>679</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>에너지 충전 효과 — 하나만 먹어도 에너지가 도는 기분이 들고 피로 개선에 좋음</t>
+          <t>원활한 배변 활동 — 복용 후 변비가 개선되고 배변 활동이 원활해짐</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>휴대성과 뛰어난 맛 — 맛이 좋고 여행 등 외출 시 간편하게 챙겨 먹기 편함</t>
+          <t>편안한 소화 상태 — 소화가 잘되고 속이 편안하게 유지됨</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>빛바랜 포장 및 소비기한 — 배송받은 제품의 포장이 빛바래 있거나 소비기한에 아쉬움이 있음</t>
+          <t>체감 효과의 부족 — 체중 감량이나 배변 관련 효과를 크게 체감하기 어려움</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -4543,7 +5046,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4558,43 +5061,43 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>83</v>
+        <v>2634</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>체지방 감소 효과 — 급찐살을 빼는 데 유용하며 체지방 감량 체감이 있음</t>
+          <t>꾸준한 재구매 만족도 — 만족도가 높아 주기적으로 재구매하게 됨</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>수면 유도에 도움 — 자기 전 복용 시 잠에 일찍 들 수 있어 만족스러움</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>뛰어난 다이소 가성비 — 가격이 매우 저렴하면서 품질이 우수함</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>간편한 섭취 방식 — 사무실에 두고 간식 먹은 후 간편하게 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>효과 체감의 불확실 — 다이어트나 체중 변화 관련 효과를 직접 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4602,12 +5105,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>종근당건강 브이퍼센트 멀티비타민 타우린샷 5포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4617,34 +5120,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591440&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250514/waK43E1bo4dCUhjXdTRE591591440_00_00waK43E1bo4dCUhjXdTRE.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1477</v>
+        <v>357</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>탁월한 장 건강 효과 — 지속 복용 시 유산균 효과가 매우 뛰어나 장 건강에 도움됨</t>
+          <t>단기 피로 회복 — 피곤할 때 복용하면 졸음이 감소하고 단기 에너지를 냄</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>유명 브랜드 가성비 — 믿을 수 있는 동국제약 제품을 저렴한 가격으로 구매 가능함</t>
+          <t>휴대성 높은 포장 — 액상 형태의 낱개 포장으로 여행 시 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>미비한 즉각적 효과 — 복용 초기에는 효과를 바로 알기 어려움</t>
+          <t>개당 다소 높은 가격 — 5포 구성 가격이 개당 기준으로 살짝 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -4653,7 +5156,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4661,12 +5164,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4676,39 +5179,43 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2686</v>
+        <v>1228</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>장 건강 및 아연 보충 — 장 건강 관리와 아연 섭취를 동시에 간편하게 할 수 있음</t>
+          <t>익숙한 이온음료 맛 — 포카리스웨트나 이프로 같은 익숙한 맛으로 마시기 편함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 가격이 매우 저렴하여 여러 통째 지속 재구매하기 좋음</t>
+          <t>효과적인 수분 보충 — 땀을 많이 흘린 날 시원하게 수분을 채우기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>아쉬운 맛의 호불호 — 생각했던 것보다 맛이 없다는 느낌을 받음</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4716,56 +5223,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>211</v>
+        <v>4606</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>간편한 섭취 방식 — 필름 형태로 섭취가 편리하고 가성비가 뛰어남</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 장기 복용 가능함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>피부 톤 개선 느낌 — 복용 후 피부가 다소 맑아지는 듯한 체감이 있음</t>
+          <t>브랜드 신뢰성 — 믿을 수 있는 대웅제약 브랜드 제품을 저렴하게 구매함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>강한 신맛 거부감 — 신맛이 지나치게 강하여 복용하기 부담스러움</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>아쉬운 제품 품질 — 가격이 저렴한 만큼 전반적인 품질 만족도가 떨어짐</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -4779,7 +5278,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 알파CD ZERO 15포 15일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4794,43 +5293,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000207&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/sucQSlMc1DA4dsj6Qff6600000207_00_00sucQSlMc1DA4dsj6Qff6.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>552</v>
+        <v>3542</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>기름진 식후 케어 — 기름진 음식 섭취 후 가볍게 챙겨 먹기 좋음</t>
+          <t>체중 유지 도움 — 여행이나 식후 복용 시 체중이 늘지 않도록 도와줌</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 — 섭취 후 배변 활동이 원활해지는 효과가 있음</t>
+          <t>식후 복용의 간편함 — 식사 후 가볍게 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>가루 섭취 시 기침 주의 — 복용 중 사례가 들리거나 기침이 날 수 있어 주의가 필요함</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4838,7 +5333,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4848,33 +5343,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2871</v>
+        <v>1525</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>부담 없는 알맞은 용량 — 원하는 양만큼 부담 없이 적절하게 구입 가능함</t>
+          <t>비린내 없는 식물성 — 식물성 오메가3로 어취가 없어 섭취하기 편함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 가격이 저렴하여 필요한 영양소를 부담 없이 챙길 수 있음</t>
+          <t>우수한 가성비 — 유명 제약사 제품 대비 가격이 매우 합리적임</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -4893,51 +5388,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/RhgSqjNOPs6aCmkpEpj2030086178_00_00RhgSqjNOPs6aCmkpEpj2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>804</v>
+        <v>211</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>물 없이 간편한 섭취 — 파우더 타입으로 물 없이 바로 먹을 수 있어 편리함</t>
+          <t>피부 톤 개선 느낌 — 복용 후 피부가 조금 더 맑아진 느낌을 받음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>상큼하고 달콤한 맛 — 사무실 등에서 간식 대신 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>알찬 소포장 가성비 — 가격이 저렴하여 10개입 소포장으로 여러 개 쟁여두기 좋음</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>부담 없는 저렴한 가격 — 가격대가 저렴하여 구매 부담이 적음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>강한 신맛과 저품질 — 신맛이 지나치게 강하고 전반적인 품질 만족도가 낮음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -4952,49 +5447,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2633</v>
+        <v>9</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>높은 재구매 만족도 — 제품에 만족하여 여러 번 재구매하며 사무실 등에서 먹기 좋음</t>
+          <t>입안의 시원한 개운함 — 캡슐을 터트리면 민트향으로 입안이 화하고 개운해짐</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>저렴한 가성비 — 다이어트 보조제를 저렴한 가격에 부담 없이 구입 가능함</t>
+          <t>프로폴리스 성분 함유 — 프로폴리스가 함유되어 있어 구강 관리에 도움 됨</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>효과 체감의 불확실성 — 복용 후 체감되는 효과를 확실히 알기 어려움</t>
+          <t>부족한 청량감 및 식감 — 시원함이 다소 부족하고 삼키거나 씹을 때 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5003,7 +5498,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5011,56 +5506,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 데일리버닝 14포 7일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314174&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260625/KRdkveXe1tokHnITW5go286314174_00_00KRdkveXe1tokHnITW5go.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>487</v>
+        <v>6076</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 — 식후 복용 시 화장실을 잘 가게 도와줌</t>
+          <t>부담 없는 저렴한 가격 — 가격이 저렴하여 지속적으로 구매하여 복용하기 좋음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>저렴한 가격대 — 유명 보조제를 다이소에서 저렴하게 구매할 수 있음</t>
+          <t>높은 재구매 만족도 — 매번 꾸준히 재구매하여 챙겨 먹는 영양제임</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>잘 녹지 않는 제형 — 물에 분말이 잘 녹지 않아 섭취하기 불편함</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>인공적인 사카린 맛 — 특유의 사카린 맛이 강하게 느껴져 맛에 대한 아쉬움이 있음</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5184,42 +5671,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
     </row>
@@ -5231,52 +5718,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>종근당건강</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
         </is>
       </c>
     </row>
@@ -5288,52 +5775,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
+          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>종근당건강 브이퍼센트 멀티비타민 타우린샷 5포</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 알파CD ZERO 15포 15일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 데일리버닝 14포 7일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5344,10 +5831,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
@@ -5356,7 +5843,7 @@
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
@@ -5365,13 +5852,13 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5381,37 +5868,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>254</v>
+        <v>679</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>83</v>
+        <v>2634</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1477</v>
+        <v>357</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2686</v>
+        <v>1228</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>4606</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>3542</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1525</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>552</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>2871</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>804</v>
-      </c>
       <c r="K7" s="3" t="n">
-        <v>2633</v>
+        <v>9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>6076</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5419,68 +5906,66 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>에너지 충전 효과 — 하나만 먹어도 에너지가 도는 기분이 들고 피로 개선에 좋음
-휴대성과 뛰어난 맛 — 맛이 좋고 여행 등 외출 시 간편하게 챙겨 먹기 편함</t>
+          <t>원활한 배변 활동 — 복용 후 변비가 개선되고 배변 활동이 원활해짐
+편안한 소화 상태 — 소화가 잘되고 속이 편안하게 유지됨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>체지방 감소 효과 — 급찐살을 빼는 데 유용하며 체지방 감량 체감이 있음
-수면 유도에 도움 — 자기 전 복용 시 잠에 일찍 들 수 있어 만족스러움
-뛰어난 다이소 가성비 — 가격이 매우 저렴하면서 품질이 우수함</t>
+          <t>꾸준한 재구매 만족도 — 만족도가 높아 주기적으로 재구매하게 됨
+간편한 섭취 방식 — 사무실에 두고 간식 먹은 후 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>탁월한 장 건강 효과 — 지속 복용 시 유산균 효과가 매우 뛰어나 장 건강에 도움됨
-유명 브랜드 가성비 — 믿을 수 있는 동국제약 제품을 저렴한 가격으로 구매 가능함</t>
+          <t>단기 피로 회복 — 피곤할 때 복용하면 졸음이 감소하고 단기 에너지를 냄
+휴대성 높은 포장 — 액상 형태의 낱개 포장으로 여행 시 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>장 건강 및 아연 보충 — 장 건강 관리와 아연 섭취를 동시에 간편하게 할 수 있음
-뛰어난 가성비 — 가격이 매우 저렴하여 여러 통째 지속 재구매하기 좋음</t>
+          <t>익숙한 이온음료 맛 — 포카리스웨트나 이프로 같은 익숙한 맛으로 마시기 편함
+효과적인 수분 보충 — 땀을 많이 흘린 날 시원하게 수분을 채우기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>간편한 섭취 방식 — 필름 형태로 섭취가 편리하고 가성비가 뛰어남
-피부 톤 개선 느낌 — 복용 후 피부가 다소 맑아지는 듯한 체감이 있음</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 장기 복용 가능함
+브랜드 신뢰성 — 믿을 수 있는 대웅제약 브랜드 제품을 저렴하게 구매함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>기름진 식후 케어 — 기름진 음식 섭취 후 가볍게 챙겨 먹기 좋음
-원활한 배변 활동 — 섭취 후 배변 활동이 원활해지는 효과가 있음</t>
+          <t>체중 유지 도움 — 여행이나 식후 복용 시 체중이 늘지 않도록 도와줌
+식후 복용의 간편함 — 식사 후 가볍게 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 알맞은 용량 — 원하는 양만큼 부담 없이 적절하게 구입 가능함
-저렴한 가성비 — 가격이 저렴하여 필요한 영양소를 부담 없이 챙길 수 있음</t>
+          <t>비린내 없는 식물성 — 식물성 오메가3로 어취가 없어 섭취하기 편함
+우수한 가성비 — 유명 제약사 제품 대비 가격이 매우 합리적임</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>물 없이 간편한 섭취 — 파우더 타입으로 물 없이 바로 먹을 수 있어 편리함
-상큼하고 달콤한 맛 — 사무실 등에서 간식 대신 맛있게 먹기 좋음
-알찬 소포장 가성비 — 가격이 저렴하여 10개입 소포장으로 여러 개 쟁여두기 좋음</t>
+          <t>피부 톤 개선 느낌 — 복용 후 피부가 조금 더 맑아진 느낌을 받음
+부담 없는 저렴한 가격 — 가격대가 저렴하여 구매 부담이 적음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>높은 재구매 만족도 — 제품에 만족하여 여러 번 재구매하며 사무실 등에서 먹기 좋음
-저렴한 가성비 — 다이어트 보조제를 저렴한 가격에 부담 없이 구입 가능함</t>
+          <t>입안의 시원한 개운함 — 캡슐을 터트리면 민트향으로 입안이 화하고 개운해짐
+프로폴리스 성분 함유 — 프로폴리스가 함유되어 있어 구강 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 — 식후 복용 시 화장실을 잘 가게 도와줌
-저렴한 가격대 — 유명 보조제를 다이소에서 저렴하게 구매할 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>부담 없는 저렴한 가격 — 가격이 저렴하여 지속적으로 구매하여 복용하기 좋음
+높은 재구매 만족도 — 매번 꾸준히 재구매하여 챙겨 먹는 영양제임</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -5488,40 +5973,38 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>빛바랜 포장 및 소비기한 — 배송받은 제품의 포장이 빛바래 있거나 소비기한에 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>체감 효과의 부족 — 체중 감량이나 배변 관련 효과를 크게 체감하기 어려움</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>효과 체감의 불확실 — 다이어트나 체중 변화 관련 효과를 직접 느끼기 어려움</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>미비한 즉각적 효과 — 복용 초기에는 효과를 바로 알기 어려움</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>강한 신맛 거부감 — 신맛이 지나치게 강하여 복용하기 부담스러움
-아쉬운 제품 품질 — 가격이 저렴한 만큼 전반적인 품질 만족도가 떨어짐</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>가루 섭취 시 기침 주의 — 복용 중 사례가 들리거나 기침이 날 수 있어 주의가 필요함</t>
-        </is>
-      </c>
+          <t>개당 다소 높은 가격 — 5포 구성 가격이 개당 기준으로 살짝 비싸게 느껴짐</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 맛의 호불호 — 생각했던 것보다 맛이 없다는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛과 저품질 — 신맛이 지나치게 강하고 전반적인 품질 만족도가 낮음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>효과 체감의 불확실성 — 복용 후 체감되는 효과를 확실히 알기 어려움</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>잘 녹지 않는 제형 — 물에 분말이 잘 녹지 않아 섭취하기 불편함
-인공적인 사카린 맛 — 특유의 사카린 맛이 강하게 느껴져 맛에 대한 아쉬움이 있음</t>
-        </is>
-      </c>
+          <t>부족한 청량감 및 식감 — 시원함이 다소 부족하고 삼키거나 씹을 때 아쉬움이 남음</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5551,32 +6034,32 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -5664,7 +6147,1145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>리뷰평점</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>리뷰건수</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>긍정1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>긍정2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>긍정3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>부정1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>부정2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>부정3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8145</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[독일1위] 도펠헤르츠 3종 (마그네슘400+B1+B6+B12+엽산/이뮨플러스/마칼디)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>도펠헤르츠</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000243640&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024364021ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>759</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>13,950원</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12501</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>빠른 수면 유도 — 섭취 후 잠이 푹 들고 빠르게 숙면을 취하게 됨</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>맛있는 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 간식처럼 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>자기 전 양치 번거로움 — 젤리 제형 특성상 취침 전 복용 후 다시 양치해야 함</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[키즈 3종 영양] 캔틴나인 어린이 면역 눈건강 뼈건강 츄어블(헤이뮨/헤이눈/헤이본)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>캔틴나인</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13,400원</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264034&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026403405ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24316</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역 관리 — 아침 공복 복용 시 장 건강과 면역력 유지에 효과적임</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>알찬 더블기획 구성 — 60캡슐 더블기획 및 증정 혜택으로 알차게 구성됨</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>53,900원</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41085</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>비타민 탄산수 활용 — 진한 액상을 탄산수에 타서 에이드처럼 상큼하게 마심</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>체감되는 피로 회복 — 피로할 때 섭취하면 체력과 컨디션 회복에 뛰어남</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>부담스러운 높은 가격 — 제품 효과는 우수하나 가격대가 높게 형성되어 있음</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25151</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,200원</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>물 없이 편한 섭취 — 물 없이도 간식처럼 언제 어디서나 씹어 먹기 편함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>상큼한 레몬라임 맛 — 상큼한 맛으로 피로를 풀어주는 느낌을 제공함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>합리적인 세일 가격 — 세일 프로모션 기간에 합리적인 가격으로 구매 가능함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>490</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>도펠헤르츠</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>캔틴나인</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[독일1위] 도펠헤르츠 3종 (마그네슘400+B1+B6+B12+엽산/이뮨플러스/마칼디)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[키즈 3종 영양] 캔틴나인 어린이 면역 눈건강 뼈건강 츄어블(헤이뮨/헤이눈/헤이본)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>평점</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>리뷰수</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>8145</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>759</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>12501</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>24316</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>41085</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>25151</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>긍정리뷰</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>빠른 수면 유도 — 섭취 후 잠이 푹 들고 빠르게 숙면을 취하게 됨
+맛있는 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 간식처럼 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역 관리 — 아침 공복 복용 시 장 건강과 면역력 유지에 효과적임
+알찬 더블기획 구성 — 60캡슐 더블기획 및 증정 혜택으로 알차게 구성됨</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>비타민 탄산수 활용 — 진한 액상을 탄산수에 타서 에이드처럼 상큼하게 마심
+체감되는 피로 회복 — 피로할 때 섭취하면 체력과 컨디션 회복에 뛰어남</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>물 없이 편한 섭취 — 물 없이도 간식처럼 언제 어디서나 씹어 먹기 편함
+상큼한 레몬라임 맛 — 상큼한 맛으로 피로를 풀어주는 느낌을 제공함
+합리적인 세일 가격 — 세일 프로모션 기간에 합리적인 가격으로 구매 가능함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>부정리뷰</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>자기 전 양치 번거로움 — 젤리 제형 특성상 취침 전 복용 후 다시 양치해야 함</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>부담스러운 높은 가격 — 제품 효과는 우수하나 가격대가 높게 형성되어 있음</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>13,950원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>13,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>53,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>9,200원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5693,43 +7314,54 @@
           <t>다이소몰</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>33.3</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -5739,10 +7371,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -5750,56 +7382,65 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -5807,24 +7448,52 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily/2026-09/2026-09-16.xlsx
+++ b/data/daily/2026-09/2026-09-16.xlsx
@@ -1170,14 +1170,64 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1267,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,160 +1317,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,27 +1425,77 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1453,204 +1503,154 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용 우수한 구성 — 선물로 받을 때 만족도가 높고 다양한 감사 및 응원 선물로 적합함</t>
+          <t>선물용으로 높은 만족도 — 선물로 주고받을 때 반응이 매우 좋고 만족도가 높음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>면역력 강화 기대 — 피로 회복과 면역력 증진에 도움을 줄 것으로 기대됨</t>
+          <t>면역력 및 건강 관리 — 지속적인 섭취를 통해 면역력 증진 및 건강 유지에 도움됨</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -2651,21 +2651,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15392</v>
+        <v>15393</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>달콤하고 맛있는 풍미 — 비타민 특유의 신맛 없이 달콤한 과일 맛이 남</t>
+          <t>맛있는 과일 맛 — 특유의 신맛 대신 달달한 과일 맛이 나 섭취하기 편함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 네이비와 오렌지 컬러의 패키지가 깔끔하고 고급스러움</t>
+          <t>깔끔한 패키지 구성 — 추석 카드와 함께 포장이 깔끔하게 제공됨</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>편리한 휴대성 — 작은 용기로 구성되어 편리하게 휴대하며 섭취 가능함</t>
+          <t>피로회복 기획 선물 — 건강과 피로회복을 챙겨줄 수 있는 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2714,18 +2714,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 복용 후 피로감이 줄어들고 힘이 나는 느낌을 받음</t>
+          <t>피로회복 효과 체감 — 섭취 후 피로감이 줄어들고 컨디션 유지에 도움이 됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 포장 상태 — 포장이 고급스럽게 잘 되어 있어 선물용으로 우수함</t>
+          <t>고급스러운 선물 포장 — 패키지 포장이 고급스러워 선물용 만족도가 높음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>구매 후 가격 인하 — 구매 직후 제품 가격이 내려가 아쉬움이 남음</t>
+          <t>구매 직후 가격 하락 — 제품 구매 후 가격이 추가 할인되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2773,17 +2773,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 느낌 — 복용 후 피로가 덜하고 생기 회복에 도움이 됨</t>
+          <t>피로감 개선 효과 — 꾸준히 섭취 시 지친 몸의 피로감이 줄어드는 느낌을 받음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 일체형 구성 — 여러 영양제를 따로 챙길 필요 없이 한 번에 간편하게 섭취함</t>
+          <t>한 번에 챙기는 간편함 — 여러 영양제를 따로 챙길 필요 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>알찬 추가 증정 혜택 — 7입 구성에 2입이 추가 증정되어 더욱 실용적임</t>
+          <t>풍성한 추가 증정 — 기본 수량에 증정분이 추가되어 구성이 알참</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2832,17 +2832,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 선물 포장이 예쁘고 고급스러워 선물용으로 적합함</t>
+          <t>쉬운 목넘김과 편의성 — 알약 크기가 크지 않아 삼키기 쉽고 챙겨 먹기 간편함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>쉬운 알약 목넘김 — 알약 크기가 크지 않아 쉽게 삼킬 수 있음</t>
+          <t>컨디션 회복 도움 — 체력이 떨어지거나 피곤한 날 섭취하면 에너지가 충전됨</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 — 피로할 때 섭취하면 컨디션 회복에 도움을 줌</t>
+          <t>깔끔한 선물용 포장 — 선물 포장이 이쁘게 잘 되어 있어 받거나 줄 때 만족함</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2891,23 +2891,23 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 알약 거부감 없이 맛있는 젤리처럼 손이 자주 감</t>
+          <t>젤리 형태의 섭취 편의성 — 알약 거부감 없이 맛있는 젤리 형태로 간편히 먹기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간편한 복용 방법 — 하루 2개씩 씹어 먹으면 되어 복용이 간편함</t>
+          <t>남녀노소 뛰어난 기호성 — 맛이 좋아 아이부터 성인까지 거부감 없이 잘 챙겨 먹음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>약간의 씁쓸한 맛 — 달지 않고 약간 씁쓸한 맛이 느껴짐</t>
+          <t>약간의 씁쓸한 맛 — 완전히 달지만은 않고 끝맛에 약간의 씁쓸함이 느껴짐</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>효과 체감의 불확실성 — 실제 효과가 있는지 직접 체감하기 어려움</t>
+          <t>효과 체감의 불확실성 — 섭취 후 즉각적인 영양 효과 체감은 명확하지 않음</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+올레샷1박스+쇼핑백증정</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2954,20 +2954,16 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>우수한 컨디션 회복 — 피로감이 심할 때 섭취 시 컨디션 회복에 효과적임</t>
+          <t>우수한 컨디션 회복 — 피로감이 심할 때 복용하면 빠른 회복감을 느낌</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>편리한 휴대 및 섭취 — 휴대하기 편하고 간편하게 마시기 좋은 형태임</t>
+          <t>높은 휴대성과 마시기 편함 — 가방에 지니고 다니기 쉬우며 간편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 가격대가 높아 지속적 구매에 부담이 될 수 있음</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -3009,21 +3005,21 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 포장이 고급스러워 선물용으로 만족도가 매우 높음</t>
+          <t>고급스러운 포장 디자인 — 패키지가 깔끔하고 고급스러워 선물용으로 만족스러움</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 상큼한 맛 — 쓴맛 없이 달달하고 새콤하여 부담 없이 먹기 좋음</t>
+          <t>부담 없는 맛과 제형 — 쓴맛이 심하지 않고 달달새콤하여 분말과 액상을 함께 먹기 편함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>높은 브랜드 신뢰도 — 정관장 브랜드 제품으로 믿고 먹을 수 있음</t>
+          <t>높은 브랜드 신뢰도 — 정관장 브랜드 제품이라 안심하고 선물하거나 먹기 좋음</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3068,16 +3064,16 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>체감되는 피로 개선 — 피로감이 덜해지고 개운한 상태를 유지하는 데 도움 됨</t>
+          <t>빠른 피로 회복 도움 — 지친 날 먹으면 개운해지고 피로감이 덜 느껴짐</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 명절 패키지가 고급스럽고 젤리까지 동봉되어 구성이 알참</t>
+          <t>귀엽고 고급스러운 포장 — 시즌 패키지 구성이 고급스럽고 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -3127,18 +3123,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>효과적인 피로 감소 — 꾸준히 복용 시 피로함이 덜하고 효과를 체감함</t>
+          <t>피로 개선 지속력 — 꾸준한 복용 시 덜 피로하고 활력이 오래 유지됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>우수한 휴대성 — 하루 하나씩 가지고 다니며 먹기 편함</t>
+          <t>우수한 휴대성과 편의성 — 하루 하나씩 챙겨 다니며 간편하게 먹기 좋음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 약간 힘듦</t>
+          <t>알약의 큰 크기 — 기존 제품 대비 알약이 커서 삼키기가 다소 힘들 수 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3182,22 +3178,22 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>맛있는 말차베리 풍미 — 말차향이 과하지 않고 맛있게 즐길 수 있음</t>
+          <t>은은하고 맛있는 말차 맛 — 말차향이 과하지 않고 맛있게 즐길 수 있음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>만족스러운 굿즈 구성 — 포토카드와 엽서 등 만족스러운 굿즈가 동봉됨</t>
+          <t>포토카드 등 굿즈 만족 — 함께 증정되는 아티스트 포토카드와 엽서의 만족도가 높음</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>기존 대비 적은 용량 — 기존 효소 제품에 비해 용량이 절반 수준으로 적음</t>
+          <t>적은 제품 1포 용량 — 기존에 먹던 일반 효소에 비해 1포당 용량이 다소 적음</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3245,17 +3241,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>우수한 소화 및 배변 — 식후 복용 시 소화가 잘되고 배변 활동에 도움을 줌</t>
+          <t>소화 및 배변 활동 개선 — 식후 더부룩함이 감소하고 장 운동과 소화에 도움을 줌</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>고소한 군고구마 맛 — 고소하고 군고구마 맛이 나 부담 없이 먹기 좋음</t>
+          <t>고소한 군고구마 맛 — 군고구마 맛이 나 고소하고 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>합리적인 가격 혜택 — 할인 행사 및 사은품 증정 혜택으로 가격 부담이 적음</t>
+          <t>개별 포장의 섭취 편의 — 한 포씩 낱개 포장되어 휴대와 섭취가 간편함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -3304,12 +3300,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>정성스러운 고급 포장 — 포장이 예쁘고 고급스러워 선물용으로 매우 만족스러움</t>
+          <t>정성스럽고 예쁜 포장 — 은은하고 고급스러운 핑크색 패키지로 선물 시 미소를 짓게 함</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>피부 개선 기대감 — 복용 시 피부가 맑아지고 탱탱해지는 느낌을 받음</t>
+          <t>피부 상태 개선 체감 — 꾸준히 먹으면 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -3359,23 +3355,23 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>맛과 소화 촉진 효과 — 맛이 좋고 식후 소화 관리에 도움을 줌</t>
+          <t>좋은 맛과 소화 돕기 — 맛이 나쁘지 않고 식후 소화를 도와 속을 편하게 해줌</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>보너스 증정 혜택 — 추가 증정 10포와 과자 사은품 구성이 알참</t>
+          <t>풍성한 구성과 혜택 — 증정 포수와 과자 사은품 구성이 혜택으로 제공됨</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>구매 수량 제한 — 구매 수량이 최대 2개로 제한되어 있어 아쉬움</t>
+          <t>구매 수량制限 — 추가 구매 시 수량이 ograničenje(2개 이상 불가)되어 아쉬움</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>복용 초기 장 반응 — 복용 직후 뱃속이 꾸르룩거리고 방귀가 자주 나옴</t>
+          <t>섭취 초기 장 반응 — 복용 직후 뱃속에서 소리가 나거나 가스가 찰 수 있음</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -3391,7 +3387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3401,46 +3397,46 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>부드럽고 맛있는 식감 — 닭가슴살의 뻑뻑함 없이 부드럽고 맛있음</t>
+          <t>다양한 맛과 식단 구성 — 여러 맛이 골고루 들어있어 한 달 점심 식단으로 골라 먹기 좋음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>다양한 맛 구성 — 다양한 맛으로 구성되어 매일 먹어도 물리지 않음</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 24팩의 닭가슴살을 저렴한 가격에 구매 가능함</t>
-        </is>
-      </c>
+          <t>가성비와 보냉백 증정 — 가격 대비 양과 맛이 훌륭하며 도시락 보냉백이 제공됨</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>배송 중 제품 융해 — 배송 시 제품이 완전히 녹아서 도착하는 문제 있음</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>배송 중 포장 파손 — 비닐 포장이 헐렁하거나 해동되어 주변으로 소스가 새어 나옴</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>생각보다 큰 보냉백 크기 — 증정 보냉가방이 사진으로 본 것보다 커서 예상과 다름</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
@@ -3454,7 +3450,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3464,46 +3460,42 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>다양하고 알찬 구성 — 종류가 다양하여 매일 하나씩 골라 먹는 재미가 있음</t>
+          <t>부드럽고 맛있는 식감 — 뻑뻑함이 적고 부드러우며 양념 맛이 다양해 물리지 않음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>유용한 증정 사은품 — 도시락 싸기에 용이한 보냉백을 증정하여 유용함</t>
+          <t>뛰어난 가성비 구성 — 저렴한 가격에 다량의 닭가슴살 식단을 구성할 수 있음</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>포장 불량 및 터짐 — 일부 포장이 터져 소스가 새고 진공 상태가 헐렁함</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>배송 중 제품 해동 — 도착 시 제품이 많이 녹아 있음</t>
-        </is>
-      </c>
+          <t>배송 시 제품 해동 — 배송 과정에서 제품이 완전히 녹아서 도착하는 경우가 있음</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
@@ -3548,17 +3540,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤함 — 단백질 특유의 텁텁함과 비린 맛 없이 음료처럼 맛있음</t>
+          <t>비린 맛없는 달콤한 맛 — 특유의 비리고 텁텁한 맛이 없으며 모카라떼나 초코우유처럼 맛있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>부드러운 목넘김 — 목넘김이 부드럽고 마신 후 속이 더부룩하지 않음</t>
+          <t>속 편한 포만감 — 과하게 달지 않고 담백하여 마신 후 속 더부룩함 없이 간식으로 좋음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>알찬 영양 성분 — 당과 칼로리가 낮고 팩당 단백질 함량이 20g으로 충분함</t>
+          <t>충분한 단백질 함량 — 한 팩당 20g의 단백질이 들어있어 운동 후 보충용으로 적합함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3607,17 +3599,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 섭취 후 에너지가 생기고 피로 회복에 도움이 됨</t>
+          <t>운동 및 피로회복 도움 — 웨이트 트레이닝 시 활력을 주며 피로회복에 유용함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 — 부담 없는 레몬맛으로 맛있게 섭취 가능함</t>
+          <t>상큼한 레몬 맛 — 레몬 맛 액상이라 물에 타서 부담 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>편리한 액상 제형 — 물에 타 먹거나 간편하게 챙기기 좋은 액상 스틱 제형임</t>
+          <t>간편한 휴대와 섭취 — 스틱 형태 액상이라 외출 시에도 들고 다니며 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3666,17 +3658,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>고함량으로 인한 활력 — 6,200mg 고함량 아르기닌으로 운동 및 일상 활력 증진에 효과적임</t>
+          <t>초고함량으로 활력 증진 — 6,200mg 고함량 함유로 피로 개선과 운동 지구력 향상에 도움됨</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>알찬 추가 증정 구성 — 쇼핑백과 추가 5포 증정으로 선물용으로 적합함</t>
+          <t>고급스러운 선물 포장 — 블랙/레드 패키지와 쇼핑백, 추가 5포 구성으로 선물하기 좋음</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>편리한 개별 포장 — 개별 포장되어 있어 휴대와 복용이 용이함</t>
+          <t>1포 포장의 휴대성 — 개별 포장되어 하루 한 포씩 필요할 때 먹기 편리함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3725,19 +3717,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>알찬 세트 조합 — 아르기닌과 밀크씨슬/마카 세트로 건강을 한 번에 관리함</t>
+          <t>간 건강과 활력 동시 관리 — 아르기닌과 밀크씨슬(마카) 조합으로 피로감을 줄이고 활력을 얻음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>피로 감소 및 활력 — 아침에 일어날 때 몸이 가볍고 피로감이 감소함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>넉넉한 2개월 용량 — 2개월분의 넉넉한 용량 구성으로 만족스러움</t>
-        </is>
-      </c>
+          <t>넉넉한 2개월분 구성 — 2개월용 세트에 쇼핑백이 포함되어 본인 및 선물용 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3997,7 +3985,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+올레샷1박스+쇼핑백증정</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -4063,7 +4051,7 @@
         <v>16055</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15392</v>
+        <v>15393</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3349</v>
@@ -4081,10 +4069,10 @@
         <v>734</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>769</v>
@@ -4098,66 +4086,66 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용 우수한 구성 — 선물로 받을 때 만족도가 높고 다양한 감사 및 응원 선물로 적합함
-면역력 강화 기대 — 피로 회복과 면역력 증진에 도움을 줄 것으로 기대됨</t>
+          <t>선물용으로 높은 만족도 — 선물로 주고받을 때 반응이 매우 좋고 만족도가 높음
+면역력 및 건강 관리 — 지속적인 섭취를 통해 면역력 증진 및 건강 유지에 도움됨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>달콤하고 맛있는 풍미 — 비타민 특유의 신맛 없이 달콤한 과일 맛이 남
-고급스러운 포장 디자인 — 네이비와 오렌지 컬러의 패키지가 깔끔하고 고급스러움
-편리한 휴대성 — 작은 용기로 구성되어 편리하게 휴대하며 섭취 가능함</t>
+          <t>맛있는 과일 맛 — 특유의 신맛 대신 달달한 과일 맛이 나 섭취하기 편함
+깔끔한 패키지 구성 — 추석 카드와 함께 포장이 깔끔하게 제공됨
+피로회복 기획 선물 — 건강과 피로회복을 챙겨줄 수 있는 선물용으로 적합함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 복용 후 피로감이 줄어들고 힘이 나는 느낌을 받음
-고급스러운 포장 상태 — 포장이 고급스럽게 잘 되어 있어 선물용으로 우수함</t>
+          <t>피로회복 효과 체감 — 섭취 후 피로감이 줄어들고 컨디션 유지에 도움이 됨
+고급스러운 선물 포장 — 패키지 포장이 고급스러워 선물용 만족도가 높음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 느낌 — 복용 후 피로가 덜하고 생기 회복에 도움이 됨
-간편한 일체형 구성 — 여러 영양제를 따로 챙길 필요 없이 한 번에 간편하게 섭취함
-알찬 추가 증정 혜택 — 7입 구성에 2입이 추가 증정되어 더욱 실용적임</t>
+          <t>피로감 개선 효과 — 꾸준히 섭취 시 지친 몸의 피로감이 줄어드는 느낌을 받음
+한 번에 챙기는 간편함 — 여러 영양제를 따로 챙길 필요 없이 간편하게 섭취 가능함
+풍성한 추가 증정 — 기본 수량에 증정분이 추가되어 구성이 알참</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 선물 포장이 예쁘고 고급스러워 선물용으로 적합함
-쉬운 알약 목넘김 — 알약 크기가 크지 않아 쉽게 삼킬 수 있음
-빠른 컨디션 회복 — 피로할 때 섭취하면 컨디션 회복에 도움을 줌</t>
+          <t>쉬운 목넘김과 편의성 — 알약 크기가 크지 않아 삼키기 쉽고 챙겨 먹기 간편함
+컨디션 회복 도움 — 체력이 떨어지거나 피곤한 날 섭취하면 에너지가 충전됨
+깔끔한 선물용 포장 — 선물 포장이 이쁘게 잘 되어 있어 받거나 줄 때 만족함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 알약 거부감 없이 맛있는 젤리처럼 손이 자주 감
-간편한 복용 방법 — 하루 2개씩 씹어 먹으면 되어 복용이 간편함</t>
+          <t>젤리 형태의 섭취 편의성 — 알약 거부감 없이 맛있는 젤리 형태로 간편히 먹기 좋음
+남녀노소 뛰어난 기호성 — 맛이 좋아 아이부터 성인까지 거부감 없이 잘 챙겨 먹음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>우수한 컨디션 회복 — 피로감이 심할 때 섭취 시 컨디션 회복에 효과적임
-편리한 휴대 및 섭취 — 휴대하기 편하고 간편하게 마시기 좋은 형태임</t>
+          <t>우수한 컨디션 회복 — 피로감이 심할 때 복용하면 빠른 회복감을 느낌
+높은 휴대성과 마시기 편함 — 가방에 지니고 다니기 쉬우며 간편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 포장이 고급스러워 선물용으로 만족도가 매우 높음
-부담 없는 상큼한 맛 — 쓴맛 없이 달달하고 새콤하여 부담 없이 먹기 좋음
-높은 브랜드 신뢰도 — 정관장 브랜드 제품으로 믿고 먹을 수 있음</t>
+          <t>고급스러운 포장 디자인 — 패키지가 깔끔하고 고급스러워 선물용으로 만족스러움
+부담 없는 맛과 제형 — 쓴맛이 심하지 않고 달달새콤하여 분말과 액상을 함께 먹기 편함
+높은 브랜드 신뢰도 — 정관장 브랜드 제품이라 안심하고 선물하거나 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 개선 — 피로감이 덜해지고 개운한 상태를 유지하는 데 도움 됨
-고급스러운 패키지 — 명절 패키지가 고급스럽고 젤리까지 동봉되어 구성이 알참</t>
+          <t>빠른 피로 회복 도움 — 지친 날 먹으면 개운해지고 피로감이 덜 느껴짐
+귀엽고 고급스러운 포장 — 시즌 패키지 구성이 고급스럽고 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>효과적인 피로 감소 — 꾸준히 복용 시 피로함이 덜하고 효과를 체감함
-우수한 휴대성 — 하루 하나씩 가지고 다니며 먹기 편함</t>
+          <t>피로 개선 지속력 — 꾸준한 복용 시 덜 피로하고 활력이 오래 유지됨
+우수한 휴대성과 편의성 — 하루 하나씩 챙겨 다니며 간편하게 먹기 좋음</t>
         </is>
       </c>
     </row>
@@ -4171,27 +4159,23 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>구매 후 가격 인하 — 구매 직후 제품 가격이 내려가 아쉬움이 남음</t>
+          <t>구매 직후 가격 하락 — 제품 구매 후 가격이 추가 할인되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>약간의 씁쓸한 맛 — 달지 않고 약간 씁쓸한 맛이 느껴짐
-효과 체감의 불확실성 — 실제 효과가 있는지 직접 체감하기 어려움</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 가격대가 높아 지속적 구매에 부담이 될 수 있음</t>
-        </is>
-      </c>
+          <t>약간의 씁쓸한 맛 — 완전히 달지만은 않고 끝맛에 약간의 씁쓸함이 느껴짐
+효과 체감의 불확실성 — 섭취 후 즉각적인 영양 효과 체감은 명확하지 않음</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 약간 힘듦</t>
+          <t>알약의 큰 크기 — 기존 제품 대비 알약이 커서 삼키기가 다소 힘들 수 있음</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4509,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -4598,7 +4582,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1655</v>
@@ -4610,10 +4594,10 @@
         <v>863</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>51</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>145</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>213</v>
@@ -4636,68 +4620,66 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 말차베리 풍미 — 말차향이 과하지 않고 맛있게 즐길 수 있음
-만족스러운 굿즈 구성 — 포토카드와 엽서 등 만족스러운 굿즈가 동봉됨</t>
+          <t>은은하고 맛있는 말차 맛 — 말차향이 과하지 않고 맛있게 즐길 수 있음
+포토카드 등 굿즈 만족 — 함께 증정되는 아티스트 포토카드와 엽서의 만족도가 높음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>우수한 소화 및 배변 — 식후 복용 시 소화가 잘되고 배변 활동에 도움을 줌
-고소한 군고구마 맛 — 고소하고 군고구마 맛이 나 부담 없이 먹기 좋음
-합리적인 가격 혜택 — 할인 행사 및 사은품 증정 혜택으로 가격 부담이 적음</t>
+          <t>소화 및 배변 활동 개선 — 식후 더부룩함이 감소하고 장 운동과 소화에 도움을 줌
+고소한 군고구마 맛 — 군고구마 맛이 나 고소하고 부담 없이 먹기 좋음
+개별 포장의 섭취 편의 — 한 포씩 낱개 포장되어 휴대와 섭취가 간편함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>정성스러운 고급 포장 — 포장이 예쁘고 고급스러워 선물용으로 매우 만족스러움
-피부 개선 기대감 — 복용 시 피부가 맑아지고 탱탱해지는 느낌을 받음</t>
+          <t>정성스럽고 예쁜 포장 — 은은하고 고급스러운 핑크색 패키지로 선물 시 미소를 짓게 함
+피부 상태 개선 체감 — 꾸준히 먹으면 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>맛과 소화 촉진 효과 — 맛이 좋고 식후 소화 관리에 도움을 줌
-보너스 증정 혜택 — 추가 증정 10포와 과자 사은품 구성이 알참</t>
+          <t>좋은 맛과 소화 돕기 — 맛이 나쁘지 않고 식후 소화를 도와 속을 편하게 해줌
+풍성한 구성과 혜택 — 증정 포수와 과자 사은품 구성이 혜택으로 제공됨</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 맛있는 식감 — 닭가슴살의 뻑뻑함 없이 부드럽고 맛있음
-다양한 맛 구성 — 다양한 맛으로 구성되어 매일 먹어도 물리지 않음
-뛰어난 가성비 — 24팩의 닭가슴살을 저렴한 가격에 구매 가능함</t>
+          <t>다양한 맛과 식단 구성 — 여러 맛이 골고루 들어있어 한 달 점심 식단으로 골라 먹기 좋음
+가성비와 보냉백 증정 — 가격 대비 양과 맛이 훌륭하며 도시락 보냉백이 제공됨</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>다양하고 알찬 구성 — 종류가 다양하여 매일 하나씩 골라 먹는 재미가 있음
-유용한 증정 사은품 — 도시락 싸기에 용이한 보냉백을 증정하여 유용함</t>
+          <t>부드럽고 맛있는 식감 — 뻑뻑함이 적고 부드러우며 양념 맛이 다양해 물리지 않음
+뛰어난 가성비 구성 — 저렴한 가격에 다량의 닭가슴살 식단을 구성할 수 있음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤함 — 단백질 특유의 텁텁함과 비린 맛 없이 음료처럼 맛있음
-부드러운 목넘김 — 목넘김이 부드럽고 마신 후 속이 더부룩하지 않음
-알찬 영양 성분 — 당과 칼로리가 낮고 팩당 단백질 함량이 20g으로 충분함</t>
+          <t>비린 맛없는 달콤한 맛 — 특유의 비리고 텁텁한 맛이 없으며 모카라떼나 초코우유처럼 맛있음
+속 편한 포만감 — 과하게 달지 않고 담백하여 마신 후 속 더부룩함 없이 간식으로 좋음
+충분한 단백질 함량 — 한 팩당 20g의 단백질이 들어있어 운동 후 보충용으로 적합함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 섭취 후 에너지가 생기고 피로 회복에 도움이 됨
-상큼한 레몬맛 — 부담 없는 레몬맛으로 맛있게 섭취 가능함
-편리한 액상 제형 — 물에 타 먹거나 간편하게 챙기기 좋은 액상 스틱 제형임</t>
+          <t>운동 및 피로회복 도움 — 웨이트 트레이닝 시 활력을 주며 피로회복에 유용함
+상큼한 레몬 맛 — 레몬 맛 액상이라 물에 타서 부담 없이 맛있게 먹을 수 있음
+간편한 휴대와 섭취 — 스틱 형태 액상이라 외출 시에도 들고 다니며 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>고함량으로 인한 활력 — 6,200mg 고함량 아르기닌으로 운동 및 일상 활력 증진에 효과적임
-알찬 추가 증정 구성 — 쇼핑백과 추가 5포 증정으로 선물용으로 적합함
-편리한 개별 포장 — 개별 포장되어 있어 휴대와 복용이 용이함</t>
+          <t>초고함량으로 활력 증진 — 6,200mg 고함량 함유로 피로 개선과 운동 지구력 향상에 도움됨
+고급스러운 선물 포장 — 블랙/레드 패키지와 쇼핑백, 추가 5포 구성으로 선물하기 좋음
+1포 포장의 휴대성 — 개별 포장되어 하루 한 포씩 필요할 때 먹기 편리함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>알찬 세트 조합 — 아르기닌과 밀크씨슬/마카 세트로 건강을 한 번에 관리함
-피로 감소 및 활력 — 아침에 일어날 때 몸이 가볍고 피로감이 감소함
-넉넉한 2개월 용량 — 2개월분의 넉넉한 용량 구성으로 만족스러움</t>
+          <t>간 건강과 활력 동시 관리 — 아르기닌과 밀크씨슬(마카) 조합으로 피로감을 줄이고 활력을 얻음
+넉넉한 2개월분 구성 — 2개월용 세트에 쇼핑백이 포함되어 본인 및 선물용 만족도가 높음</t>
         </is>
       </c>
     </row>
@@ -4709,26 +4691,26 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>기존 대비 적은 용량 — 기존 효소 제품에 비해 용량이 절반 수준으로 적음</t>
+          <t>적은 제품 1포 용량 — 기존에 먹던 일반 효소에 비해 1포당 용량이 다소 적음</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>구매 수량 제한 — 구매 수량이 최대 2개로 제한되어 있어 아쉬움
-복용 초기 장 반응 — 복용 직후 뱃속이 꾸르룩거리고 방귀가 자주 나옴</t>
+          <t>구매 수량制限 — 추가 구매 시 수량이 ograničenje(2개 이상 불가)되어 아쉬움
+섭취 초기 장 반응 — 복용 직후 뱃속에서 소리가 나거나 가스가 찰 수 있음</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 제품 융해 — 배송 시 제품이 완전히 녹아서 도착하는 문제 있음</t>
+          <t>배송 중 포장 파손 — 비닐 포장이 헐렁하거나 해동되어 주변으로 소스가 새어 나옴
+생각보다 큰 보냉백 크기 — 증정 보냉가방이 사진으로 본 것보다 커서 예상과 다름</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>포장 불량 및 터짐 — 일부 포장이 터져 소스가 새고 진공 상태가 헐렁함
-배송 중 제품 해동 — 도착 시 제품이 많이 녹아 있음</t>
+          <t>배송 시 제품 해동 — 배송 과정에서 제품이 완전히 녹아서 도착하는 경우가 있음</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -4764,12 +4746,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>46,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>33,000원</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>46,900원</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -4979,7 +4961,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4987,49 +4969,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235549&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/kQh0cYBVEEUhZLYsuKrQ968235549_00_00kQh0cYBVEEUhZLYsuKrQ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>679</v>
+        <v>7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 — 복용 후 변비가 개선되고 배변 활동이 원활해짐</t>
+          <t>저렴한 가성비 — 타 판매처 대비 대폭 저렴한 가격으로 구매 만족감이 큼</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>편안한 소화 상태 — 소화가 잘되고 속이 편안하게 유지됨</t>
+          <t>상쾌한 구강 정돈 — 섭취 후 트름 시 상쾌한 향이 남으며 구강 케어에 도움됨</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>체감 효과의 부족 — 체중 감량이나 배변 관련 효과를 크게 체감하기 어려움</t>
+          <t>약한 청량감과 맛 호불호 — 스트롱민트 제품치고 강도가 약하며 맛에 대한 호불호가 있음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -5046,49 +5028,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2634</v>
+        <v>11</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>꾸준한 재구매 만족도 — 만족도가 높아 주기적으로 재구매하게 됨</t>
+          <t>개운한 캡슐 섭취 — 톡 깨물어 터트리면 입안이 시원하고 개운한 민트 맛이 머묾</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 섭취 방식 — 사무실에 두고 간식 먹은 후 간편하게 챙겨 먹기 좋음</t>
+          <t>부담 없는 가성비 — 저렴한 가격에 프로폴리스 함유 민트볼을 구매할 수 있음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>효과 체감의 불확실 — 다이어트나 체중 변화 관련 효과를 직접 느끼기 어려움</t>
+          <t>아쉬운 청량감 및 크기 — 기존 민트볼 대비 알이 크고 목의 시원함이 다소 적을 수 있음</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5097,7 +5079,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5105,12 +5087,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 타우린샷 5포</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5120,36 +5102,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591440&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250514/waK43E1bo4dCUhjXdTRE591591440_00_00waK43E1bo4dCUhjXdTRE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>357</v>
+        <v>3542</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>단기 피로 회복 — 피곤할 때 복용하면 졸음이 감소하고 단기 에너지를 냄</t>
+          <t>체중 유지 보조 도움 — 여행이나 식후 섭취 시 체중이 늘지 않도록 돕는 느낌을 받음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>휴대성 높은 포장 — 액상 형태의 낱개 포장으로 여행 시 챙겨 먹기 편함</t>
+          <t>부담 없는 가격 — 다이소에서 저렴하게 살 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>개당 다소 높은 가격 — 5포 구성 가격이 개당 기준으로 살짝 비싸게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -5164,12 +5142,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5179,36 +5157,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1228</v>
+        <v>2637</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>익숙한 이온음료 맛 — 포카리스웨트나 이프로 같은 익숙한 맛으로 마시기 편함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>효과적인 수분 보충 — 땀을 많이 흘린 날 시원하게 수분을 채우기 좋음</t>
-        </is>
-      </c>
+          <t>재구매를 부르는 만족도 — 실제 체감 효과가 좋아 주기적으로 계속 구매하게 됨</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>아쉬운 맛의 호불호 — 생각했던 것보다 맛이 없다는 느낌을 받음</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -5223,43 +5193,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>4606</v>
+        <v>1191</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 장기 복용 가능함</t>
+          <t>뜻밖의 쾌변 완화 효과 — 섭취 후 화장실을 잘 가 변비 해소에 도움을 줌</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>브랜드 신뢰성 — 믿을 수 있는 대웅제약 브랜드 제품을 저렴하게 구매함</t>
+          <t>식후 심리적 안심과 가성비 — 가격이 착하고 저녁마다 간편히 먹으면 유지 관리에 도움이 됨</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5270,7 +5240,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5278,7 +5248,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5293,28 +5263,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3542</v>
+        <v>6395</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>체중 유지 도움 — 여행이나 식후 복용 시 체중이 늘지 않도록 도와줌</t>
+          <t>시중 대비 뛰어난 가성비 — 영양 성분이 양호하면서 일반 약국/시중보다 저렴함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>식후 복용의 간편함 — 식사 후 가볍게 챙겨 먹기 편함</t>
+          <t>안정감과 브랜드 신뢰 — 유명 제약사 제품이라 믿음이 가며 먹었을 때 안정이 됨</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -5325,7 +5295,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5333,7 +5303,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5343,33 +5313,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1525</v>
+        <v>662</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>비린내 없는 식물성 — 식물성 오메가3로 어취가 없어 섭취하기 편함</t>
+          <t>우수한 가성비 — 다이소 매장에서 부담 없는 가격으로 구매 가능함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 유명 제약사 제품 대비 가격이 매우 합리적임</t>
+          <t>간편한 휴대성과 복용 — 가지고 다니기 편하여 과식한 날 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5380,7 +5350,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5388,49 +5358,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000269&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/LdyaPluhRl2HSeYjB2pX600000269_00_01LdyaPluhRl2HSeYjB2pX.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>211</v>
+        <v>480</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>피부 톤 개선 느낌 — 복용 후 피부가 조금 더 맑아진 느낌을 받음</t>
+          <t>여행용 휴대 편의성 — 낱개 포장으로 여행이나 외출 시 하나씩 들고 가기 좋음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 가격대가 저렴하여 구매 부담이 적음</t>
+          <t>편안한 목넘김과 눈 안구 건조 완화 — 목넘김이 편하며 안구 건조 개선에 다소 도움을 받음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>강한 신맛과 저품질 — 신맛이 지나치게 강하고 전반적인 품질 만족도가 낮음</t>
+          <t>소용량 대비 아쉬운 가성비 — 6캡슐 구성으로 다른 제품에 비해 상대적으로 가성비가 낮음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -5447,58 +5417,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>3681</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>입안의 시원한 개운함 — 캡슐을 터트리면 민트향으로 입안이 화하고 개운해짐</t>
+          <t>좋은 성분과 저렴한 가격 — 성분이 양호하고 가격이 싸 부담 없이 복용하기에 좋음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>프로폴리스 성분 함유 — 프로폴리스가 함유되어 있어 구강 관리에 도움 됨</t>
+          <t>쉬운 구매 접근성 — 다이소에서 간편하게 장기적으로 구매하여 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>부족한 청량감 및 식감 — 시원함이 다소 부족하고 삼키거나 씹을 때 아쉬움이 남음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5506,7 +5472,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5516,33 +5482,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>6076</v>
+        <v>1528</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 가격이 저렴하여 지속적으로 구매하여 복용하기 좋음</t>
+          <t>비린내 없는 식물성 원료 — 식물성 오메가3로 어취가 없어 부담 없이 복용하기 편함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>높은 재구매 만족도 — 매번 꾸준히 재구매하여 챙겨 먹는 영양제임</t>
+          <t>합리적인 대형 제약사 가격 — 유명 제약사 제품을 저렴한 가격으로 꾸준히 챙길 수 있음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -5661,7 +5627,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -5671,7 +5637,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5686,27 +5652,27 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
         </is>
       </c>
     </row>
@@ -5718,47 +5684,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5775,52 +5741,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 타우린샷 5포</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 바나바잎 10정 10일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 밀크씨슬 30정 30일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5831,19 +5797,19 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
@@ -5852,10 +5818,10 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5868,34 +5834,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>679</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2634</v>
+        <v>11</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>357</v>
+        <v>3542</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1228</v>
+        <v>2637</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4606</v>
+        <v>1191</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3542</v>
+        <v>6395</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1525</v>
+        <v>662</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>211</v>
+        <v>480</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>9</v>
+        <v>3681</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6076</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5906,62 +5872,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 — 복용 후 변비가 개선되고 배변 활동이 원활해짐
-편안한 소화 상태 — 소화가 잘되고 속이 편안하게 유지됨</t>
+          <t>저렴한 가성비 — 타 판매처 대비 대폭 저렴한 가격으로 구매 만족감이 큼
+상쾌한 구강 정돈 — 섭취 후 트름 시 상쾌한 향이 남으며 구강 케어에 도움됨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>꾸준한 재구매 만족도 — 만족도가 높아 주기적으로 재구매하게 됨
-간편한 섭취 방식 — 사무실에 두고 간식 먹은 후 간편하게 챙겨 먹기 좋음</t>
+          <t>개운한 캡슐 섭취 — 톡 깨물어 터트리면 입안이 시원하고 개운한 민트 맛이 머묾
+부담 없는 가성비 — 저렴한 가격에 프로폴리스 함유 민트볼을 구매할 수 있음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>단기 피로 회복 — 피곤할 때 복용하면 졸음이 감소하고 단기 에너지를 냄
-휴대성 높은 포장 — 액상 형태의 낱개 포장으로 여행 시 챙겨 먹기 편함</t>
+          <t>체중 유지 보조 도움 — 여행이나 식후 섭취 시 체중이 늘지 않도록 돕는 느낌을 받음
+부담 없는 가격 — 다이소에서 저렴하게 살 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>익숙한 이온음료 맛 — 포카리스웨트나 이프로 같은 익숙한 맛으로 마시기 편함
-효과적인 수분 보충 — 땀을 많이 흘린 날 시원하게 수분을 채우기 좋음</t>
+          <t>재구매를 부르는 만족도 — 실제 체감 효과가 좋아 주기적으로 계속 구매하게 됨</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 장기 복용 가능함
-브랜드 신뢰성 — 믿을 수 있는 대웅제약 브랜드 제품을 저렴하게 구매함</t>
+          <t>뜻밖의 쾌변 완화 효과 — 섭취 후 화장실을 잘 가 변비 해소에 도움을 줌
+식후 심리적 안심과 가성비 — 가격이 착하고 저녁마다 간편히 먹으면 유지 관리에 도움이 됨</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>체중 유지 도움 — 여행이나 식후 복용 시 체중이 늘지 않도록 도와줌
-식후 복용의 간편함 — 식사 후 가볍게 챙겨 먹기 편함</t>
+          <t>시중 대비 뛰어난 가성비 — 영양 성분이 양호하면서 일반 약국/시중보다 저렴함
+안정감과 브랜드 신뢰 — 유명 제약사 제품이라 믿음이 가며 먹었을 때 안정이 됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>비린내 없는 식물성 — 식물성 오메가3로 어취가 없어 섭취하기 편함
-우수한 가성비 — 유명 제약사 제품 대비 가격이 매우 합리적임</t>
+          <t>우수한 가성비 — 다이소 매장에서 부담 없는 가격으로 구매 가능함
+간편한 휴대성과 복용 — 가지고 다니기 편하여 과식한 날 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>피부 톤 개선 느낌 — 복용 후 피부가 조금 더 맑아진 느낌을 받음
-부담 없는 저렴한 가격 — 가격대가 저렴하여 구매 부담이 적음</t>
+          <t>여행용 휴대 편의성 — 낱개 포장으로 여행이나 외출 시 하나씩 들고 가기 좋음
+편안한 목넘김과 눈 안구 건조 완화 — 목넘김이 편하며 안구 건조 개선에 다소 도움을 받음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>입안의 시원한 개운함 — 캡슐을 터트리면 민트향으로 입안이 화하고 개운해짐
-프로폴리스 성분 함유 — 프로폴리스가 함유되어 있어 구강 관리에 도움 됨</t>
+          <t>좋은 성분과 저렴한 가격 — 성분이 양호하고 가격이 싸 부담 없이 복용하기에 좋음
+쉬운 구매 접근성 — 다이소에서 간편하게 장기적으로 구매하여 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 가격이 저렴하여 지속적으로 구매하여 복용하기 좋음
-높은 재구매 만족도 — 매번 꾸준히 재구매하여 챙겨 먹는 영양제임</t>
+          <t>비린내 없는 식물성 원료 — 식물성 오메가3로 어취가 없어 부담 없이 복용하기 편함
+합리적인 대형 제약사 가격 — 유명 제약사 제품을 저렴한 가격으로 꾸준히 챙길 수 있음</t>
         </is>
       </c>
     </row>
@@ -5973,37 +5938,25 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>체감 효과의 부족 — 체중 감량이나 배변 관련 효과를 크게 체감하기 어려움</t>
+          <t>약한 청량감과 맛 호불호 — 스트롱민트 제품치고 강도가 약하며 맛에 대한 호불호가 있음</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>효과 체감의 불확실 — 다이어트나 체중 변화 관련 효과를 직접 느끼기 어려움</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>개당 다소 높은 가격 — 5포 구성 가격이 개당 기준으로 살짝 비싸게 느껴짐</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>아쉬운 맛의 호불호 — 생각했던 것보다 맛이 없다는 느낌을 받음</t>
-        </is>
-      </c>
+          <t>아쉬운 청량감 및 크기 — 기존 민트볼 대비 알이 크고 목의 시원함이 다소 적을 수 있음</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>강한 신맛과 저품질 — 신맛이 지나치게 강하고 전반적인 품질 만족도가 낮음</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>부족한 청량감 및 식감 — 시원함이 다소 부족하고 삼키거나 씹을 때 아쉬움이 남음</t>
-        </is>
-      </c>
+          <t>소용량 대비 아쉬운 가성비 — 6캡슐 구성으로 다른 제품에 비해 상대적으로 가성비가 낮음</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -6014,52 +5967,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6191,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6246,34 +6199,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>8145</v>
+        <v>22081</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -6322,7 +6275,11 @@
       <c r="J3" t="n">
         <v>759</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>오프라인 직접 구매 가능 — 오프라인 웰니스 매장에서 제품을 직접 확인하고 살 수 있음</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -6332,7 +6289,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6340,37 +6297,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>12501</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>8146</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>넉넉한 2개월용 구성 — 1일 1캡슐로 총 60캡슐이 들어있어 두 달간 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>이너뷰티 루틴 형성 — 아침 공복에 물과 함께 먹으며 건강 관리 루틴을 만들기 적합함</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -6379,7 +6344,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6387,54 +6352,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15505</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>빠른 수면 유도 — 섭취 후 잠이 푹 들고 빠르게 숙면을 취하게 됨</t>
+          <t>필수 영양소 집중 구성 — 비타민 B 없이 C와 D로만 구성되어 트러블 걱정 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 간식처럼 챙겨 먹기 좋음</t>
+          <t>브랜드 신뢰도와 가성비 — 대한민국 대표 비타민 브랜드 제품으로 가성비와 효과가 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>자기 전 양치 번거로움 — 젤리 제형 특성상 취침 전 복용 후 다시 양치해야 함</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6442,34 +6407,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[키즈 3종 영양] 캔틴나인 어린이 면역 눈건강 뼈건강 츄어블(헤이뮨/헤이눈/헤이본)</t>
+          <t>(임박특가) 솔가 남성용 멀티비타민&amp;미네랄 60정 (2개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>캔틴나인</t>
+          <t>솔가</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13,400원</t>
+          <t>45,220원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264034&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000233620&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026403405ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/B00000023362002ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -6481,7 +6446,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6489,54 +6454,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>53,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>24316</v>
+        <v>41086</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>장 건강 및 면역 관리 — 아침 공복 복용 시 장 건강과 면역력 유지에 효과적임</t>
+          <t>탁월한 피로 회복 체감 — 지치거나 피곤할 때 복용하면 확실한 컨디션 회복 효과가 나타남</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>알찬 더블기획 구성 — 60캡슐 더블기획 및 증정 혜택으로 알차게 구성됨</t>
+          <t>탄산수 조작 등 상쾌한 섭취 — 꾸덕한 액상을 탄산수에 타서 상큼하게 에이드처럼 즐길 수 있음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>다소 비싼 가격대 — 제품 효능은 뛰어나지만 가격이 높다는 단점이 있음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6544,58 +6513,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[키즈 3종 영양] 캔틴나인 어린이 면역 눈건강 뼈건강 츄어블(헤이뮨/헤이눈/헤이본)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>캔틴나인</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53,900원</t>
+          <t>13,400원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264034&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026403405ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>41085</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>비타민 탄산수 활용 — 진한 액상을 탄산수에 타서 에이드처럼 상큼하게 마심</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>체감되는 피로 회복 — 피로할 때 섭취하면 체력과 컨디션 회복에 뛰어남</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>부담스러운 높은 가격 — 제품 효과는 우수하나 가격대가 높게 형성되어 있음</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6603,37 +6560,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>9,200원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>25151</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>4776</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>맛있는 레몬라임 구미 — 상큼하고 쫀득하여 간식처럼 맛있게 피로를 풀며 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>물 없이 간편한 섭취 — 언제 어디서나 물 없이 바로 꺼내 먹기 용이함</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6642,7 +6607,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6650,54 +6615,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9,200원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12504</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>물 없이 편한 섭취 — 물 없이도 간식처럼 언제 어디서나 씹어 먹기 편함</t>
+          <t>속 편한 장 및 피부 관리 — 복통이나 가스 차는 현상 없이 화장실을 잘 가며 피부 면역을 도움</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>상큼한 레몬라임 맛 — 상큼한 맛으로 피로를 풀어주는 느낌을 제공함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>합리적인 세일 가격 — 세일 프로모션 기간에 합리적인 가격으로 구매 가능함</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>귀여운 콜라보 증정품 — 산리오 러기지택 등 기획 구성 품목이 매력적임</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>약간 큰 알약 크기 — 기존 제품 대비 알약 크기가 다소 크게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6705,39 +6674,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>퓨레카 그린즈 워터믹스 7포 4종/크런치 2종 택 1 (마시는 3초 샐러드)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>퓨레카</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>11,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245977&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024597713ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>490</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>4220</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3초 간편 식전 야채 루틴 — 손질 과정 없이 물에 1포 타서 41종 과일과 야채를 섭취함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>상큼달콤한 과일 에이드 맛 — 거부감 없는 과일 에이드 맛으로 맛있게 식이섬유를 챙김</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>크런치 제형의 단단함 — 크런치 타입 제품의 경우 식감이 단단하고 초반 입안 텁텁함이 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6852,52 +6833,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6909,52 +6890,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>도펠헤르츠</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>도펠헤르츠</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>솔가</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>캔틴나인</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>바이오코어유산균</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>캔틴나인</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>퓨레카</t>
         </is>
       </c>
     </row>
@@ -6966,52 +6947,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[독일1위] 도펠헤르츠 3종 (마그네슘400+B1+B6+B12+엽산/이뮨플러스/마칼디)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[독일1위] 도펠헤르츠 3종 (마그네슘400+B1+B6+B12+엽산/이뮨플러스/마칼디)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>(임박특가) 솔가 남성용 멀티비타민&amp;미네랄 60정 (2개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[키즈 3종 영양] 캔틴나인 어린이 면역 눈건강 뼈건강 츄어블(헤이뮨/헤이눈/헤이본)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[키즈 3종 영양] 캔틴나인 어린이 면역 눈건강 뼈건강 츄어블(헤이뮨/헤이눈/헤이본)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>퓨레카 그린즈 워터믹스 7포 4종/크런치 2종 택 1 (마시는 3초 샐러드)</t>
         </is>
       </c>
     </row>
@@ -7028,24 +7009,28 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="L6" s="3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -7055,69 +7040,86 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8145</v>
+        <v>22081</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>759</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>12501</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>8146</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>15505</v>
+      </c>
       <c r="G7" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>41086</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>24316</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>41085</v>
-      </c>
       <c r="J7" s="3" t="n">
-        <v>25151</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
+        <v>4776</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>12504</v>
+      </c>
       <c r="L7" s="3" t="n">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>오프라인 직접 구매 가능 — 오프라인 웰니스 매장에서 제품을 직접 확인하고 살 수 있음</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>넉넉한 2개월용 구성 — 1일 1캡슐로 총 60캡슐이 들어있어 두 달간 복용하기 좋음
+이너뷰티 루틴 형성 — 아침 공복에 물과 함께 먹으며 건강 관리 루틴을 만들기 적합함</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>빠른 수면 유도 — 섭취 후 잠이 푹 들고 빠르게 숙면을 취하게 됨
-맛있는 젤리 제형 — 맛있는 젤리 형태라 거부감 없이 간식처럼 챙겨 먹기 좋음</t>
+          <t>필수 영양소 집중 구성 — 비타민 B 없이 C와 D로만 구성되어 트러블 걱정 없이 섭취 가능함
+브랜드 신뢰도와 가성비 — 대한민국 대표 비타민 브랜드 제품으로 가성비와 효과가 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>장 건강 및 면역 관리 — 아침 공복 복용 시 장 건강과 면역력 유지에 효과적임
-알찬 더블기획 구성 — 60캡슐 더블기획 및 증정 혜택으로 알차게 구성됨</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>비타민 탄산수 활용 — 진한 액상을 탄산수에 타서 에이드처럼 상큼하게 마심
-체감되는 피로 회복 — 피로할 때 섭취하면 체력과 컨디션 회복에 뛰어남</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>탁월한 피로 회복 체감 — 지치거나 피곤할 때 복용하면 확실한 컨디션 회복 효과가 나타남
+탄산수 조작 등 상쾌한 섭취 — 꾸덕한 액상을 탄산수에 타서 상큼하게 에이드처럼 즐길 수 있음</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 레몬라임 구미 — 상큼하고 쫀득하여 간식처럼 맛있게 피로를 풀며 먹을 수 있음
+물 없이 간편한 섭취 — 언제 어디서나 물 없이 바로 꺼내 먹기 용이함</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>물 없이 편한 섭취 — 물 없이도 간식처럼 언제 어디서나 씹어 먹기 편함
-상큼한 레몬라임 맛 — 상큼한 맛으로 피로를 풀어주는 느낌을 제공함
-합리적인 세일 가격 — 세일 프로모션 기간에 합리적인 가격으로 구매 가능함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>속 편한 장 및 피부 관리 — 복통이나 가스 차는 현상 없이 화장실을 잘 가며 피부 면역을 도움
+귀여운 콜라보 증정품 — 산리오 러기지택 등 기획 구성 품목이 매력적임</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>3초 간편 식전 야채 루틴 — 손질 과정 없이 물에 1포 타서 41종 과일과 야채를 섭취함
+상큼달콤한 과일 에이드 맛 — 거부감 없는 과일 에이드 맛으로 맛있게 식이섬유를 챙김</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7128,21 +7130,25 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>자기 전 양치 번거로움 — 젤리 제형 특성상 취침 전 복용 후 다시 양치해야 함</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>부담스러운 높은 가격 — 제품 효과는 우수하나 가격대가 높게 형성되어 있음</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>다소 비싼 가격대 — 제품 효능은 뛰어나지만 가격이 높다는 단점이 있음</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>약간 큰 알약 크기 — 기존 제품 대비 알약 크기가 다소 크게 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>크런치 제형의 단단함 — 크런치 타입 제품의 경우 식감이 단단하고 초반 입안 텁텁함이 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7152,52 +7158,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>31,400원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>45,220원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>53,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>13,400원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>9,200원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>13,950원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>13,400원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>30,400원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>53,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>9,200원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>11,000원</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7323,7 +7329,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -7333,32 +7339,32 @@
         <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -7380,16 +7386,16 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7402,16 +7408,16 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7424,23 +7430,23 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -7449,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7477,7 +7483,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7487,13 +7493,57 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
